--- a/media/exports/reports/2026-08/runway.xlsx
+++ b/media/exports/reports/2026-08/runway.xlsx
@@ -24,44 +24,53 @@
     <numFmt numFmtId="164" formatCode="#,##0;[Red](#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot; months&quot;;[Red](0.0&quot; months&quot;)"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
@@ -94,38 +103,38 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -664,8 +673,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 runway.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1057,8 +1066,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 runway.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1593,8 +1602,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 runway.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-08/runway.xlsx
+++ b/media/exports/reports/2026-08/runway.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>target 3.0 months</t>
         </is>
       </c>
     </row>

--- a/media/exports/reports/2026-08/runway.xlsx
+++ b/media/exports/reports/2026-08/runway.xlsx
@@ -12,7 +12,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="Runway_now">'Report'!$B$8</definedName>
+    <definedName name="Target">'Report'!$B$9</definedName>
+    <definedName name="Gap">'Report'!$B$10</definedName>
+    <definedName name="Runway_in_July">'Report'!$B$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$C$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -119,10 +126,12 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -212,6 +221,148 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Cash at bank by date</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Cash at bank</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$A$6:$A$36</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$C$6:$C$36</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="runway_Data" displayName="runway_Data" ref="A5:C36" headerRowCount="1">
+  <autoFilter ref="A5:C36"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Status"/>
+    <tableColumn id="3" name="Cash at bank"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -522,14 +673,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -627,37 +778,37 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
+          <t>Cash at bank, every day (1 Aug to 31 Aug): every month is on the Data sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Unrestricted cash ($303,775, after setting aside unspent grant money) would cover 2.2 months of spending at August's rate of spending, short of the 3.0 months target by $119,825.</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>A reserves plan is the usual next step: how much of each month's surplus goes to reserves, and by when the gap is closed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Cash at bank, every day (1 Aug to 31 Aug): every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
@@ -666,15 +817,15 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A16:D16"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -708,14 +859,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -728,7 +879,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>(Cash at bank − unspent grant money) ÷ a month's cash spending</t>
         </is>
@@ -811,7 +962,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Target months × monthly cash spending − unrestricted cash</t>
         </is>
@@ -898,7 +1049,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Target months × monthly cash spending − unrestricted cash</t>
         </is>
@@ -985,7 +1136,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>(Cash at bank − unspent grant money) ÷ a month's cash spending</t>
         </is>
@@ -1067,7 +1218,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1103,14 +1254,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1754,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1612,5 +1763,9 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="32" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/media/exports/reports/2026-08/runway.xlsx
+++ b/media/exports/reports/2026-08/runway.xlsx
@@ -17,7 +17,7 @@
     <definedName name="Gap">'Report'!$B$10</definedName>
     <definedName name="Runway_in_July">'Report'!$B$11</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$C$36</definedName>
   </definedNames>
@@ -680,7 +680,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>How long the organisation could keep going on its own money: cash at bank, less unspent grant money (which belongs to the funders' programs), divided by a month's spending.</t>
+          <t>How long the organisation could keep going on its own money: cash at bank, less unspent grant money (which belongs to the funders' programs) and GST and PAYG owed to the ATO, divided by a month's spending.</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>Workings!B12</f>
+        <f>Workings!B13</f>
         <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>Workings!B24</f>
+        <f>Workings!B25</f>
         <v/>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <f>Workings!B35</f>
+        <f>Workings!B36</f>
         <v/>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B11" s="6">
-        <f>Workings!B45</f>
+        <f>Workings!B47</f>
         <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Unrestricted cash ($303,775, after setting aside unspent grant money) would cover 2.2 months of spending at August's rate of spending, short of the 3.0 months target by $119,825.</t>
+          <t>Unrestricted cash ($273,798, after setting aside unspent grant money) would cover 1.9 months of spending at August's rate of spending, short of the 3.0 months target by $149,802.</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -866,7 +866,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>(Cash at bank − unspent grant money) ÷ a month's cash spending</t>
+          <t>(Cash at bank − unspent grant money − GST and PAYG owed to the ATO) ÷ a month's cash spending</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>525675</v>
+        <v>547394</v>
       </c>
     </row>
     <row r="9">
@@ -916,316 +916,336 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unrestricted cash</t>
-        </is>
-      </c>
-      <c r="B10" s="12">
-        <f>B8+B9</f>
-        <v/>
+          <t>Less GST and PAYG withheld owed to the ATO (paid with the BAS)</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>-51696</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Unrestricted cash</t>
+        </is>
+      </c>
+      <c r="B11" s="12">
+        <f>B8+B9+B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Cash spending in August (expenses less depreciation)</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B12" s="12" t="n">
         <v>141200</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Runway</t>
         </is>
       </c>
-      <c r="B12" s="14">
-        <f>B10/B11</f>
+      <c r="B13" s="14">
+        <f>B11/B12</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Reserves target: 3.0 months.</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15"/>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Reserves: how far from 3.0 months?</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Target months × monthly cash spending − unrestricted cash</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Unrestricted cash</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>303775</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A month's cash spending</t>
+          <t>Unrestricted cash</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>141200</v>
+        <v>273798</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Runway</t>
-        </is>
-      </c>
-      <c r="B21" s="15">
-        <f>B19/B20</f>
-        <v/>
+          <t>A month's cash spending</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>141200</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reserves target</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>3</v>
+          <t>Runway</t>
+        </is>
+      </c>
+      <c r="B22" s="15">
+        <f>B20/B21</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Reserves target</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Cash needed for the target</t>
         </is>
       </c>
-      <c r="B23" s="12">
-        <f>B22*B20</f>
+      <c r="B24" s="12">
+        <f>B23*B21</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Gap to the target</t>
         </is>
       </c>
-      <c r="B24" s="16">
-        <f>B23-B19</f>
+      <c r="B25" s="16">
+        <f>B24-B20</f>
         <v/>
       </c>
     </row>
-    <row r="25"/>
     <row r="26"/>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Reserves: how far from 3.0 months?</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Target months × monthly cash spending − unrestricted cash</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr"/>
-      <c r="B29" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Unrestricted cash</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="n">
-        <v>303775</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A month's cash spending</t>
+          <t>Unrestricted cash</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>141200</v>
+        <v>273798</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Runway</t>
-        </is>
-      </c>
-      <c r="B32" s="15">
-        <f>B30/B31</f>
-        <v/>
+          <t>A month's cash spending</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>141200</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Reserves target</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="n">
-        <v>3</v>
+          <t>Runway</t>
+        </is>
+      </c>
+      <c r="B33" s="15">
+        <f>B31/B32</f>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Reserves target</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Cash needed for the target</t>
         </is>
       </c>
-      <c r="B34" s="12">
-        <f>B33*B31</f>
+      <c r="B35" s="12">
+        <f>B34*B32</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>Gap to the target</t>
         </is>
       </c>
-      <c r="B35" s="16">
-        <f>B34-B30</f>
+      <c r="B36" s="16">
+        <f>B35-B31</f>
         <v/>
       </c>
     </row>
-    <row r="36"/>
     <row r="37"/>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Unrestricted cash runway, July 2026</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>(Cash at bank − unspent grant money) ÷ a month's cash spending</t>
-        </is>
-      </c>
-    </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr"/>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>(Cash at bank − unspent grant money − GST and PAYG owed to the ATO) ÷ a month's cash spending</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr"/>
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Cash at bank</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="n">
-        <v>610000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Less unspent grant money (belongs to funders' programs)</t>
+          <t>Cash at bank</t>
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>-290400</v>
+        <v>610000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Unrestricted cash</t>
-        </is>
-      </c>
-      <c r="B43" s="12">
-        <f>B41+B42</f>
-        <v/>
+          <t>Less unspent grant money (belongs to funders' programs)</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="n">
+        <v>-290400</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Less GST and PAYG withheld owed to the ATO (paid with the BAS)</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="n">
+        <v>-40307</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unrestricted cash</t>
+        </is>
+      </c>
+      <c r="B45" s="12">
+        <f>B42+B43+B44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Cash spending in July (expenses less depreciation)</t>
         </is>
       </c>
-      <c r="B44" s="12" t="n">
+      <c r="B46" s="12" t="n">
         <v>134918</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="13" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>Runway</t>
         </is>
       </c>
-      <c r="B45" s="14">
-        <f>B43/B44</f>
+      <c r="B47" s="14">
+        <f>B45/B46</f>
         <v/>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Reserves target: 3.0 months.</t>
         </is>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48"/>
     <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="26" min="0" max="16383" man="1"/>
+    <brk id="27" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -1261,7 +1281,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1315,7 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>610594</v>
+        <v>610000</v>
       </c>
     </row>
     <row r="7">
@@ -1310,7 +1330,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>611188</v>
+        <v>610000</v>
       </c>
     </row>
     <row r="8">
@@ -1325,7 +1345,7 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>613087</v>
+        <v>612356</v>
       </c>
     </row>
     <row r="9">
@@ -1340,7 +1360,7 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>614986</v>
+        <v>614712</v>
       </c>
     </row>
     <row r="10">
@@ -1355,7 +1375,7 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>616885</v>
+        <v>617068</v>
       </c>
     </row>
     <row r="11">
@@ -1370,7 +1390,7 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>571896</v>
+        <v>582091</v>
       </c>
     </row>
     <row r="12">
@@ -1385,7 +1405,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>573795</v>
+        <v>584447</v>
       </c>
     </row>
     <row r="13">
@@ -1400,7 +1420,7 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>574389</v>
+        <v>584447</v>
       </c>
     </row>
     <row r="14">
@@ -1415,7 +1435,7 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>574983</v>
+        <v>584447</v>
       </c>
     </row>
     <row r="15">
@@ -1430,7 +1450,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>576882</v>
+        <v>586803</v>
       </c>
     </row>
     <row r="16">
@@ -1445,7 +1465,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>578781</v>
+        <v>589159</v>
       </c>
     </row>
     <row r="17">
@@ -1460,7 +1480,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>579375</v>
+        <v>589159</v>
       </c>
     </row>
     <row r="18">
@@ -1475,7 +1495,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>581274</v>
+        <v>591515</v>
       </c>
     </row>
     <row r="19">
@@ -1490,7 +1510,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>583173</v>
+        <v>593871</v>
       </c>
     </row>
     <row r="20">
@@ -1505,7 +1525,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>583767</v>
+        <v>593871</v>
       </c>
     </row>
     <row r="21">
@@ -1520,7 +1540,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>584361</v>
+        <v>593871</v>
       </c>
     </row>
     <row r="22">
@@ -1535,7 +1555,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>568010</v>
+        <v>577977</v>
       </c>
     </row>
     <row r="23">
@@ -1550,7 +1570,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>569908</v>
+        <v>580332</v>
       </c>
     </row>
     <row r="24">
@@ -1565,7 +1585,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>571806</v>
+        <v>582687</v>
       </c>
     </row>
     <row r="25">
@@ -1580,7 +1600,7 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>526817</v>
+        <v>547709</v>
       </c>
     </row>
     <row r="26">
@@ -1595,7 +1615,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>528715</v>
+        <v>550064</v>
       </c>
     </row>
     <row r="27">
@@ -1610,7 +1630,7 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>529308</v>
+        <v>550064</v>
       </c>
     </row>
     <row r="28">
@@ -1625,7 +1645,7 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>529901</v>
+        <v>550064</v>
       </c>
     </row>
     <row r="29">
@@ -1640,7 +1660,7 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>531799</v>
+        <v>552419</v>
       </c>
     </row>
     <row r="30">
@@ -1655,7 +1675,7 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>533697</v>
+        <v>554774</v>
       </c>
     </row>
     <row r="31">
@@ -1670,7 +1690,7 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>535595</v>
+        <v>557129</v>
       </c>
     </row>
     <row r="32">
@@ -1685,7 +1705,7 @@
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>537493</v>
+        <v>559484</v>
       </c>
     </row>
     <row r="33">
@@ -1700,7 +1720,7 @@
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>539391</v>
+        <v>561839</v>
       </c>
     </row>
     <row r="34">
@@ -1715,7 +1735,7 @@
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>539984</v>
+        <v>561839</v>
       </c>
     </row>
     <row r="35">
@@ -1730,7 +1750,7 @@
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>540577</v>
+        <v>561839</v>
       </c>
     </row>
     <row r="36">
@@ -1745,7 +1765,7 @@
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>525675</v>
+        <v>547394</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +1774,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-08/runway.xlsx
+++ b/media/exports/reports/2026-08/runway.xlsx
@@ -12,11 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Runway_now">'Report'!$B$8</definedName>
-    <definedName name="Target">'Report'!$B$9</definedName>
-    <definedName name="Gap">'Report'!$B$10</definedName>
-    <definedName name="Runway_in_July">'Report'!$B$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$19</definedName>
+    <definedName name="Runway_now">'Report'!$B$9</definedName>
+    <definedName name="Target">'Report'!$B$10</definedName>
+    <definedName name="Gap">'Report'!$B$11</definedName>
+    <definedName name="Runway_in_July">'Report'!$B$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$C$36</definedName>
@@ -31,7 +31,7 @@
     <numFmt numFmtId="164" formatCode="#,##0;[Red](#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot; months&quot;;[Red](0.0&quot; months&quot;)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Roboto"/>
       <sz val="11"/>
@@ -51,6 +51,11 @@
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -112,38 +117,41 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -654,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -680,7 +688,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -688,144 +696,152 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: 1.9 months of spending in unrestricted cash, against a 3.0 months reserves target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>How long the organisation could keep going on its own money: cash at bank, less unspent grant money (which belongs to the funders' programs) and GST and PAYG owed to the ATO, divided by a month's spending.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Runway now</t>
         </is>
       </c>
-      <c r="B8" s="6">
+      <c r="B9" s="7">
         <f>Workings!B13</f>
         <v/>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>target 3.0 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="B9" s="8">
-        <f>Workings!B25</f>
-        <v/>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>reserves target</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B10" s="7">
+        <f>Workings!B23</f>
+        <v/>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>reserves target</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="B10" s="8">
+      <c r="B11" s="9">
         <f>Workings!B36</f>
         <v/>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>to reach the target</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Runway in July</t>
         </is>
       </c>
-      <c r="B11" s="6">
+      <c r="B12" s="7">
         <f>Workings!B47</f>
         <v/>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>at July's rate of spending</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Cash at bank, every day (1 Aug to 31 Aug): every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Unrestricted cash ($273,798, after setting aside unspent grant money) would cover 1.9 months of spending at August's rate of spending, short of the 3.0 months target by $149,802.</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>A reserves plan is the usual next step: how much of each month's surplus goes to reserves, and by when the gap is closed.</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21"/>
+    <row r="22"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -866,28 +882,28 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Unrestricted cash runway, August 2026</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>(Cash at bank − unspent grant money − GST and PAYG owed to the ATO) ÷ a month's cash spending</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
@@ -899,7 +915,7 @@
           <t>Cash at bank</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
         <v>547394</v>
       </c>
     </row>
@@ -909,7 +925,7 @@
           <t>Less unspent grant money (belongs to funders' programs)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <v>-221900</v>
       </c>
     </row>
@@ -919,7 +935,7 @@
           <t>Less GST and PAYG withheld owed to the ATO (paid with the BAS)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <v>-51696</v>
       </c>
     </row>
@@ -929,7 +945,7 @@
           <t>Unrestricted cash</t>
         </is>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="13">
         <f>B8+B9+B10</f>
         <v/>
       </c>
@@ -940,17 +956,17 @@
           <t>Cash spending in August (expenses less depreciation)</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="13" t="n">
         <v>141200</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Runway</t>
         </is>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="15">
         <f>B11/B12</f>
         <v/>
       </c>
@@ -965,22 +981,22 @@
     <row r="15"/>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Reserves: how far from 3.0 months?</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Target months × monthly cash spending − unrestricted cash</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
@@ -992,7 +1008,7 @@
           <t>Unrestricted cash</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="13" t="n">
         <v>273798</v>
       </c>
     </row>
@@ -1002,7 +1018,7 @@
           <t>A month's cash spending</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="13" t="n">
         <v>141200</v>
       </c>
     </row>
@@ -1012,7 +1028,7 @@
           <t>Runway</t>
         </is>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="16">
         <f>B20/B21</f>
         <v/>
       </c>
@@ -1023,7 +1039,7 @@
           <t>Reserves target</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n">
+      <c r="B23" s="16" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1033,18 +1049,18 @@
           <t>Cash needed for the target</t>
         </is>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="13">
         <f>B23*B21</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Gap to the target</t>
         </is>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="17">
         <f>B24-B20</f>
         <v/>
       </c>
@@ -1052,22 +1068,22 @@
     <row r="26"/>
     <row r="27"/>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Reserves: how far from 3.0 months?</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Target months × monthly cash spending − unrestricted cash</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr"/>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr"/>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
@@ -1079,7 +1095,7 @@
           <t>Unrestricted cash</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="13" t="n">
         <v>273798</v>
       </c>
     </row>
@@ -1089,7 +1105,7 @@
           <t>A month's cash spending</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="13" t="n">
         <v>141200</v>
       </c>
     </row>
@@ -1099,7 +1115,7 @@
           <t>Runway</t>
         </is>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="16">
         <f>B31/B32</f>
         <v/>
       </c>
@@ -1110,7 +1126,7 @@
           <t>Reserves target</t>
         </is>
       </c>
-      <c r="B34" s="15" t="n">
+      <c r="B34" s="16" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1120,18 +1136,18 @@
           <t>Cash needed for the target</t>
         </is>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="13">
         <f>B34*B32</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>Gap to the target</t>
         </is>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="17">
         <f>B35-B31</f>
         <v/>
       </c>
@@ -1139,22 +1155,22 @@
     <row r="37"/>
     <row r="38"/>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>Unrestricted cash runway, July 2026</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>(Cash at bank − unspent grant money − GST and PAYG owed to the ATO) ÷ a month's cash spending</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr"/>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr"/>
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
@@ -1166,7 +1182,7 @@
           <t>Cash at bank</t>
         </is>
       </c>
-      <c r="B42" s="12" t="n">
+      <c r="B42" s="13" t="n">
         <v>610000</v>
       </c>
     </row>
@@ -1176,7 +1192,7 @@
           <t>Less unspent grant money (belongs to funders' programs)</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="13" t="n">
         <v>-290400</v>
       </c>
     </row>
@@ -1186,7 +1202,7 @@
           <t>Less GST and PAYG withheld owed to the ATO (paid with the BAS)</t>
         </is>
       </c>
-      <c r="B44" s="12" t="n">
+      <c r="B44" s="13" t="n">
         <v>-40307</v>
       </c>
     </row>
@@ -1196,7 +1212,7 @@
           <t>Unrestricted cash</t>
         </is>
       </c>
-      <c r="B45" s="12">
+      <c r="B45" s="13">
         <f>B42+B43+B44</f>
         <v/>
       </c>
@@ -1207,17 +1223,17 @@
           <t>Cash spending in July (expenses less depreciation)</t>
         </is>
       </c>
-      <c r="B46" s="12" t="n">
+      <c r="B46" s="13" t="n">
         <v>134918</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="13" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>Runway</t>
         </is>
       </c>
-      <c r="B47" s="14">
+      <c r="B47" s="15">
         <f>B45/B46</f>
         <v/>
       </c>
@@ -1238,7 +1254,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1281,490 +1297,490 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Cash at bank</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="n">
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n">
         <v>610000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="n">
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n">
         <v>610000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="n">
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n">
         <v>612356</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="n">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n">
         <v>614712</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="n">
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n">
         <v>617068</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="n">
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
         <v>582091</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>584447</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>584447</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="n">
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>584447</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="n">
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
         <v>586803</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="n">
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="n">
         <v>589159</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="n">
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n">
         <v>589159</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="n">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="n">
         <v>591515</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="n">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n">
         <v>593871</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="n">
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="n">
         <v>593871</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="n">
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
         <v>593871</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="n">
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n">
         <v>577977</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="n">
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
         <v>580332</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="n">
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
         <v>582687</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="n">
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
         <v>547709</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="n">
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="n">
         <v>550064</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="n">
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n">
         <v>550064</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="n">
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="n">
         <v>550064</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="n">
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
         <v>552419</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="n">
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="n">
         <v>554774</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="n">
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n">
         <v>557129</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="n">
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="n">
         <v>559484</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="n">
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="n">
         <v>561839</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="n">
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="n">
         <v>561839</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="n">
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n">
         <v>561839</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="n">
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="n">
         <v>547394</v>
       </c>
     </row>
@@ -1774,7 +1790,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 runway.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
